--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/18.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/18.xlsx
@@ -426,13 +426,13 @@
         <v>-18.90653139043986</v>
       </c>
       <c r="E2">
-        <v>-29.69115701051366</v>
+        <v>-23.86328946379339</v>
       </c>
       <c r="F2">
-        <v>-4.122520461779154</v>
+        <v>-2.508209664347117</v>
       </c>
       <c r="G2">
-        <v>-19.53800477874722</v>
+        <v>-13.73226877284303</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.33936026664308</v>
       </c>
       <c r="E3">
-        <v>-29.5083945922751</v>
+        <v>-24.24437413696087</v>
       </c>
       <c r="F3">
-        <v>-4.271969538387824</v>
+        <v>-2.776116107923519</v>
       </c>
       <c r="G3">
-        <v>-19.42735870654118</v>
+        <v>-12.6419549420767</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.78882435098895</v>
       </c>
       <c r="E4">
-        <v>-29.81902073835724</v>
+        <v>-24.41588556152738</v>
       </c>
       <c r="F4">
-        <v>-4.084652474327577</v>
+        <v>-2.337700174889672</v>
       </c>
       <c r="G4">
-        <v>-19.29932216007009</v>
+        <v>-13.0293720528219</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.31613697799224</v>
       </c>
       <c r="E5">
-        <v>-30.15127714053702</v>
+        <v>-23.95981841574089</v>
       </c>
       <c r="F5">
-        <v>-4.234783297308751</v>
+        <v>-2.515895257110291</v>
       </c>
       <c r="G5">
-        <v>-19.51791549974952</v>
+        <v>-13.27179854529836</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.9129255040151</v>
       </c>
       <c r="E6">
-        <v>-30.71976818203793</v>
+        <v>-24.82560830431937</v>
       </c>
       <c r="F6">
-        <v>-4.231669464241628</v>
+        <v>-2.339080234982736</v>
       </c>
       <c r="G6">
-        <v>-19.20620601404539</v>
+        <v>-12.70310050583696</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.58389087070674</v>
       </c>
       <c r="E7">
-        <v>-31.13233707074374</v>
+        <v>-24.82958883297211</v>
       </c>
       <c r="F7">
-        <v>-4.044466714882968</v>
+        <v>-2.836463501584866</v>
       </c>
       <c r="G7">
-        <v>-19.01076661430018</v>
+        <v>-12.10522256304742</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.32580053869497</v>
       </c>
       <c r="E8">
-        <v>-31.50895666853966</v>
+        <v>-26.35159083305409</v>
       </c>
       <c r="F8">
-        <v>-3.945231613497199</v>
+        <v>-2.191205056439385</v>
       </c>
       <c r="G8">
-        <v>-18.92801092534943</v>
+        <v>-12.74582529176249</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.12645193441502</v>
       </c>
       <c r="E9">
-        <v>-31.83031303378298</v>
+        <v>-26.01208660822503</v>
       </c>
       <c r="F9">
-        <v>-3.917807682260118</v>
+        <v>-2.504700700028858</v>
       </c>
       <c r="G9">
-        <v>-18.76426156342534</v>
+        <v>-12.40367263242983</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.96591749717891</v>
       </c>
       <c r="E10">
-        <v>-32.48279141846715</v>
+        <v>-27.17074649630158</v>
       </c>
       <c r="F10">
-        <v>-3.725482308882546</v>
+        <v>-2.30225102025427</v>
       </c>
       <c r="G10">
-        <v>-18.54958928350945</v>
+        <v>-13.05477198891356</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.83783249430508</v>
       </c>
       <c r="E11">
-        <v>-32.63526966677942</v>
+        <v>-27.08411678853484</v>
       </c>
       <c r="F11">
-        <v>-3.918240090044379</v>
+        <v>-1.956735663076985</v>
       </c>
       <c r="G11">
-        <v>-17.96770893643298</v>
+        <v>-12.42596197048314</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.72146585082893</v>
       </c>
       <c r="E12">
-        <v>-33.69265023367442</v>
+        <v>-27.80785297596671</v>
       </c>
       <c r="F12">
-        <v>-3.766614063901152</v>
+        <v>-1.773157021105573</v>
       </c>
       <c r="G12">
-        <v>-17.94646302683558</v>
+        <v>-12.34327190596357</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.59886385632236</v>
       </c>
       <c r="E13">
-        <v>-33.90515566919536</v>
+        <v>-28.12307099469263</v>
       </c>
       <c r="F13">
-        <v>-3.636373170628597</v>
+        <v>-1.924281884970106</v>
       </c>
       <c r="G13">
-        <v>-17.52482113461459</v>
+        <v>-12.3901474371618</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.47147915087051</v>
       </c>
       <c r="E14">
-        <v>-34.03057175683779</v>
+        <v>-28.87311761610906</v>
       </c>
       <c r="F14">
-        <v>-3.712491851271844</v>
+        <v>-1.447698923852272</v>
       </c>
       <c r="G14">
-        <v>-16.93504944968766</v>
+        <v>-11.06443220927779</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.32819756293713</v>
       </c>
       <c r="E15">
-        <v>-35.09649302571125</v>
+        <v>-29.27280978897407</v>
       </c>
       <c r="F15">
-        <v>-3.386727258079507</v>
+        <v>-1.559874780804576</v>
       </c>
       <c r="G15">
-        <v>-16.34916273108711</v>
+        <v>-11.20459943185415</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.16264061823032</v>
       </c>
       <c r="E16">
-        <v>-35.27297218626418</v>
+        <v>-30.04669429756688</v>
       </c>
       <c r="F16">
-        <v>-3.50711389272836</v>
+        <v>-0.848436407114637</v>
       </c>
       <c r="G16">
-        <v>-16.36578047767492</v>
+        <v>-11.5464535000249</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.98477427215581</v>
       </c>
       <c r="E17">
-        <v>-36.49038902459024</v>
+        <v>-30.21038051904813</v>
       </c>
       <c r="F17">
-        <v>-3.26892512972739</v>
+        <v>-0.4510710490939225</v>
       </c>
       <c r="G17">
-        <v>-15.8928055147672</v>
+        <v>-11.66598840143547</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.79048345749048</v>
       </c>
       <c r="E18">
-        <v>-36.41901800999236</v>
+        <v>-32.01282865018813</v>
       </c>
       <c r="F18">
-        <v>-3.209305042645701</v>
+        <v>-0.6601418695190869</v>
       </c>
       <c r="G18">
-        <v>-15.70201396536095</v>
+        <v>-11.57255233630872</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.57870403465892</v>
       </c>
       <c r="E19">
-        <v>-37.47877602574138</v>
+        <v>-32.01344225841616</v>
       </c>
       <c r="F19">
-        <v>-3.149840688635738</v>
+        <v>-0.8707112065759157</v>
       </c>
       <c r="G19">
-        <v>-15.17521548460288</v>
+        <v>-11.78346269570671</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.36221290684179</v>
       </c>
       <c r="E20">
-        <v>-37.38762010820398</v>
+        <v>-32.64433114326877</v>
       </c>
       <c r="F20">
-        <v>-2.913924137420647</v>
+        <v>0.09748792728575767</v>
       </c>
       <c r="G20">
-        <v>-14.87047203226945</v>
+        <v>-10.66919594755644</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.14065307587779</v>
       </c>
       <c r="E21">
-        <v>-38.1564304616712</v>
+        <v>-33.67323666560354</v>
       </c>
       <c r="F21">
-        <v>-2.769233203173658</v>
+        <v>0.3662359921434041</v>
       </c>
       <c r="G21">
-        <v>-15.09695014735622</v>
+        <v>-10.28123415403237</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.91797472012536</v>
       </c>
       <c r="E22">
-        <v>-38.65454675285591</v>
+        <v>-33.51702921894595</v>
       </c>
       <c r="F22">
-        <v>-2.731899512696887</v>
+        <v>0.0359360874207404</v>
       </c>
       <c r="G22">
-        <v>-14.73936754364028</v>
+        <v>-10.54567436195114</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.70993030095159</v>
       </c>
       <c r="E23">
-        <v>-39.27191587855862</v>
+        <v>-34.93001952847828</v>
       </c>
       <c r="F23">
-        <v>-2.775349039708527</v>
+        <v>1.044275420519869</v>
       </c>
       <c r="G23">
-        <v>-14.82158839347684</v>
+        <v>-10.70731717963407</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.51721847671561</v>
       </c>
       <c r="E24">
-        <v>-39.6129733699723</v>
+        <v>-35.56616823589079</v>
       </c>
       <c r="F24">
-        <v>-2.561457120999069</v>
+        <v>0.930417977739883</v>
       </c>
       <c r="G24">
-        <v>-14.3621189385078</v>
+        <v>-10.23235051523977</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.34172010439867</v>
       </c>
       <c r="E25">
-        <v>-39.70905626723005</v>
+        <v>-34.75777901959654</v>
       </c>
       <c r="F25">
-        <v>-2.542084092549797</v>
+        <v>0.8260420282523396</v>
       </c>
       <c r="G25">
-        <v>-14.82759959137375</v>
+        <v>-10.26293478139535</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.19279217625379</v>
       </c>
       <c r="E26">
-        <v>-39.89024051227694</v>
+        <v>-35.96459470027065</v>
       </c>
       <c r="F26">
-        <v>-2.501185108771377</v>
+        <v>1.162715391772143</v>
       </c>
       <c r="G26">
-        <v>-14.28746458558731</v>
+        <v>-10.5126915228356</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.06245738163145</v>
       </c>
       <c r="E27">
-        <v>-40.0127244129994</v>
+        <v>-35.83868953743539</v>
       </c>
       <c r="F27">
-        <v>-2.499237617007395</v>
+        <v>0.938424977055343</v>
       </c>
       <c r="G27">
-        <v>-14.58493028850189</v>
+        <v>-10.41806109306122</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.94153384330679</v>
       </c>
       <c r="E28">
-        <v>-39.8519590572531</v>
+        <v>-35.48302092463596</v>
       </c>
       <c r="F28">
-        <v>-2.363362168660998</v>
+        <v>0.8629573931906969</v>
       </c>
       <c r="G28">
-        <v>-14.8295125435429</v>
+        <v>-10.31533588969968</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.82688559268651</v>
       </c>
       <c r="E29">
-        <v>-40.01619322408928</v>
+        <v>-36.85058837563435</v>
       </c>
       <c r="F29">
-        <v>-2.574200725123736</v>
+        <v>0.4459878922153293</v>
       </c>
       <c r="G29">
-        <v>-14.6419858095883</v>
+        <v>-10.83013658382564</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.70112183129063</v>
       </c>
       <c r="E30">
-        <v>-39.99860463104348</v>
+        <v>-35.96885146583787</v>
       </c>
       <c r="F30">
-        <v>-2.492757298815295</v>
+        <v>0.9882115146983989</v>
       </c>
       <c r="G30">
-        <v>-14.77114453383272</v>
+        <v>-10.05606032451548</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.54969052060909</v>
       </c>
       <c r="E31">
-        <v>-39.80272548784171</v>
+        <v>-36.71006756293934</v>
       </c>
       <c r="F31">
-        <v>-2.482295018517937</v>
+        <v>0.4931526470285247</v>
       </c>
       <c r="G31">
-        <v>-14.86145195420254</v>
+        <v>-10.20105422400578</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.36884001718497</v>
       </c>
       <c r="E32">
-        <v>-39.65581726255887</v>
+        <v>-35.02808136887738</v>
       </c>
       <c r="F32">
-        <v>-2.409730862400103</v>
+        <v>0.7979421492145748</v>
       </c>
       <c r="G32">
-        <v>-14.84639442846625</v>
+        <v>-10.18019877977395</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.14770228540684</v>
       </c>
       <c r="E33">
-        <v>-39.4874010499766</v>
+        <v>-35.90940165906517</v>
       </c>
       <c r="F33">
-        <v>-2.341645688829206</v>
+        <v>0.4511461360325618</v>
       </c>
       <c r="G33">
-        <v>-14.66961205450804</v>
+        <v>-9.94561440682457</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.88139754885703</v>
       </c>
       <c r="E34">
-        <v>-39.09739301877701</v>
+        <v>-33.66362497952225</v>
       </c>
       <c r="F34">
-        <v>-2.461025028716254</v>
+        <v>0.9442268623445507</v>
       </c>
       <c r="G34">
-        <v>-14.68986375397294</v>
+        <v>-10.90713044771801</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.57645386277544</v>
       </c>
       <c r="E35">
-        <v>-38.71564039569339</v>
+        <v>-34.57552605468384</v>
       </c>
       <c r="F35">
-        <v>-2.529792777027058</v>
+        <v>-0.06723127402611842</v>
       </c>
       <c r="G35">
-        <v>-15.15794969675708</v>
+        <v>-10.44184994936719</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.2345214715049</v>
       </c>
       <c r="E36">
-        <v>-38.71499282391029</v>
+        <v>-34.91021877587974</v>
       </c>
       <c r="F36">
-        <v>-2.540643561636329</v>
+        <v>0.3781843635613841</v>
       </c>
       <c r="G36">
-        <v>-15.23986211176706</v>
+        <v>-10.44762818053337</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.86253314904683</v>
       </c>
       <c r="E37">
-        <v>-38.45134280294672</v>
+        <v>-33.64412763468223</v>
       </c>
       <c r="F37">
-        <v>-2.361790755697887</v>
+        <v>0.5735548155116476</v>
       </c>
       <c r="G37">
-        <v>-15.01824840764216</v>
+        <v>-9.366688799762382</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.47654811689582</v>
       </c>
       <c r="E38">
-        <v>-37.87162567438079</v>
+        <v>-33.12288669097735</v>
       </c>
       <c r="F38">
-        <v>-2.241442225949564</v>
+        <v>0.5728200536253644</v>
       </c>
       <c r="G38">
-        <v>-15.35224066895648</v>
+        <v>-9.736925434422327</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.08671825754842</v>
       </c>
       <c r="E39">
-        <v>-37.72040181336865</v>
+        <v>-34.20350512224271</v>
       </c>
       <c r="F39">
-        <v>-2.389715020846259</v>
+        <v>0.2638265868701068</v>
       </c>
       <c r="G39">
-        <v>-15.40466474581173</v>
+        <v>-10.0060906013867</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.705936430256385</v>
       </c>
       <c r="E40">
-        <v>-37.83418425128537</v>
+        <v>-33.59531294911655</v>
       </c>
       <c r="F40">
-        <v>-2.409944581190025</v>
+        <v>0.4360839315474584</v>
       </c>
       <c r="G40">
-        <v>-15.45816178211692</v>
+        <v>-9.420175992402891</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.351972231828451</v>
       </c>
       <c r="E41">
-        <v>-36.61361333081297</v>
+        <v>-31.92081005835227</v>
       </c>
       <c r="F41">
-        <v>-2.2589108377398</v>
+        <v>0.304327954295183</v>
       </c>
       <c r="G41">
-        <v>-15.49878002380128</v>
+        <v>-10.30459973275718</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.034774168089795</v>
       </c>
       <c r="E42">
-        <v>-36.28332907906353</v>
+        <v>-31.80076700511994</v>
       </c>
       <c r="F42">
-        <v>-2.278070975766552</v>
+        <v>0.3123573195305187</v>
       </c>
       <c r="G42">
-        <v>-15.92128159607084</v>
+        <v>-10.13983647337122</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.764789234285583</v>
       </c>
       <c r="E43">
-        <v>-36.25769338770611</v>
+        <v>-31.37298017951135</v>
       </c>
       <c r="F43">
-        <v>-2.293443818027706</v>
+        <v>0.5201300882354962</v>
       </c>
       <c r="G43">
-        <v>-15.24265443131415</v>
+        <v>-10.79203503907737</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.552549280843886</v>
       </c>
       <c r="E44">
-        <v>-35.78276967615167</v>
+        <v>-32.192230940713</v>
       </c>
       <c r="F44">
-        <v>-2.196774998855809</v>
+        <v>0.4533355110781609</v>
       </c>
       <c r="G44">
-        <v>-15.36509977624794</v>
+        <v>-9.558200577300932</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.398976596041589</v>
       </c>
       <c r="E45">
-        <v>-34.88451289317521</v>
+        <v>-30.47854769283435</v>
       </c>
       <c r="F45">
-        <v>-2.372148661702493</v>
+        <v>0.08291694467051436</v>
       </c>
       <c r="G45">
-        <v>-15.66078377585575</v>
+        <v>-9.667409474463931</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.303742168606851</v>
       </c>
       <c r="E46">
-        <v>-34.7895779640784</v>
+        <v>-30.0209091665672</v>
       </c>
       <c r="F46">
-        <v>-2.290061593922075</v>
+        <v>0.08120553761633058</v>
       </c>
       <c r="G46">
-        <v>-15.34330426203933</v>
+        <v>-9.800052856004484</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.265036769393912</v>
       </c>
       <c r="E47">
-        <v>-34.15016422690636</v>
+        <v>-31.34578669309529</v>
       </c>
       <c r="F47">
-        <v>-2.119084905249452</v>
+        <v>0.2075912089962567</v>
       </c>
       <c r="G47">
-        <v>-16.12648098934462</v>
+        <v>-9.204904889552401</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.274977699729838</v>
       </c>
       <c r="E48">
-        <v>-34.44896879159148</v>
+        <v>-30.88091845807489</v>
       </c>
       <c r="F48">
-        <v>-2.095132661797504</v>
+        <v>0.08155013845589518</v>
       </c>
       <c r="G48">
-        <v>-15.78014313191289</v>
+        <v>-9.275264123451574</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.32696688535435</v>
       </c>
       <c r="E49">
-        <v>-33.25992284292347</v>
+        <v>-29.64670777389138</v>
       </c>
       <c r="F49">
-        <v>-2.247919230672053</v>
+        <v>0.2340318681262142</v>
       </c>
       <c r="G49">
-        <v>-15.72764030574021</v>
+        <v>-10.0425712226846</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.41598874093326</v>
       </c>
       <c r="E50">
-        <v>-32.74397115685954</v>
+        <v>-27.54700381617689</v>
       </c>
       <c r="F50">
-        <v>-2.115609075627305</v>
+        <v>0.2263073420951088</v>
       </c>
       <c r="G50">
-        <v>-15.762334301899</v>
+        <v>-10.64033432271956</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.533771961865353</v>
       </c>
       <c r="E51">
-        <v>-32.77955590561182</v>
+        <v>-27.72148591969242</v>
       </c>
       <c r="F51">
-        <v>-2.183683480421966</v>
+        <v>0.3115264670255107</v>
       </c>
       <c r="G51">
-        <v>-16.30703676809618</v>
+        <v>-9.54733973393917</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.673443731936777</v>
       </c>
       <c r="E52">
-        <v>-32.10457326934652</v>
+        <v>-28.51131518526624</v>
       </c>
       <c r="F52">
-        <v>-2.054242790060515</v>
+        <v>0.2938739576718533</v>
       </c>
       <c r="G52">
-        <v>-16.2706348961157</v>
+        <v>-10.13327074903077</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.830686600633427</v>
       </c>
       <c r="E53">
-        <v>-31.88858317307668</v>
+        <v>-28.41749426077533</v>
       </c>
       <c r="F53">
-        <v>-2.096216994727769</v>
+        <v>0.1314675581485934</v>
       </c>
       <c r="G53">
-        <v>-16.03236899257662</v>
+        <v>-9.731019235615326</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.000161688244402</v>
       </c>
       <c r="E54">
-        <v>-31.73224213643587</v>
+        <v>-26.58905495306831</v>
       </c>
       <c r="F54">
-        <v>-2.099693652717318</v>
+        <v>-0.08828174646605946</v>
       </c>
       <c r="G54">
-        <v>-16.33806728038385</v>
+        <v>-10.11238905502647</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.178189214108812</v>
       </c>
       <c r="E55">
-        <v>-31.11847541180627</v>
+        <v>-27.1418321897626</v>
       </c>
       <c r="F55">
-        <v>-2.268478481242134</v>
+        <v>0.217134001476507</v>
       </c>
       <c r="G55">
-        <v>-16.46439102920091</v>
+        <v>-10.23531345830794</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.363387393102835</v>
       </c>
       <c r="E56">
-        <v>-30.71343963961221</v>
+        <v>-26.08935596021791</v>
       </c>
       <c r="F56">
-        <v>-2.186672230011266</v>
+        <v>0.2649622785793449</v>
       </c>
       <c r="G56">
-        <v>-16.20456093757316</v>
+        <v>-9.987502481252442</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.55300637883597</v>
       </c>
       <c r="E57">
-        <v>-30.46893827099008</v>
+        <v>-26.12693776600757</v>
       </c>
       <c r="F57">
-        <v>-2.293209390052714</v>
+        <v>0.1047477392038925</v>
       </c>
       <c r="G57">
-        <v>-16.48223759326273</v>
+        <v>-10.02412091385584</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.742218693868022</v>
       </c>
       <c r="E58">
-        <v>-30.01723430990998</v>
+        <v>-26.75114262322485</v>
       </c>
       <c r="F58">
-        <v>-2.244761494132582</v>
+        <v>0.5100090953080919</v>
       </c>
       <c r="G58">
-        <v>-16.72315308321106</v>
+        <v>-9.518356703904596</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.927251416994231</v>
       </c>
       <c r="E59">
-        <v>-29.88923925632018</v>
+        <v>-24.96765294851797</v>
       </c>
       <c r="F59">
-        <v>-2.336559512976017</v>
+        <v>0.4428003344493568</v>
       </c>
       <c r="G59">
-        <v>-16.6039249760163</v>
+        <v>-9.862494502280716</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.10462148514578</v>
       </c>
       <c r="E60">
-        <v>-29.63290045664199</v>
+        <v>-26.32103721892434</v>
       </c>
       <c r="F60">
-        <v>-2.330771709932657</v>
+        <v>0.08391264228867937</v>
       </c>
       <c r="G60">
-        <v>-16.73232245685893</v>
+        <v>-10.1867480980066</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.26865720141385</v>
       </c>
       <c r="E61">
-        <v>-29.08129156624167</v>
+        <v>-25.47524507156373</v>
       </c>
       <c r="F61">
-        <v>-2.348912127686563</v>
+        <v>-0.06270755963943032</v>
       </c>
       <c r="G61">
-        <v>-17.16714009425186</v>
+        <v>-10.50513815080576</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.41598491289671</v>
       </c>
       <c r="E62">
-        <v>-28.96427126940946</v>
+        <v>-24.78806725479578</v>
       </c>
       <c r="F62">
-        <v>-2.582476115477704</v>
+        <v>-0.3932510043785171</v>
       </c>
       <c r="G62">
-        <v>-17.16576854364002</v>
+        <v>-11.38190352004031</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.5470285901028</v>
       </c>
       <c r="E63">
-        <v>-29.37256754288904</v>
+        <v>-24.69268400677222</v>
       </c>
       <c r="F63">
-        <v>-2.584707737260846</v>
+        <v>-0.154038379267687</v>
       </c>
       <c r="G63">
-        <v>-16.96424247790204</v>
+        <v>-11.52491228048714</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.65759186860115</v>
       </c>
       <c r="E64">
-        <v>-28.47549042739156</v>
+        <v>-24.36415227446375</v>
       </c>
       <c r="F64">
-        <v>-2.579641442225324</v>
+        <v>0.009135916837967994</v>
       </c>
       <c r="G64">
-        <v>-17.35058826980808</v>
+        <v>-11.52592289672745</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.745363173514</v>
       </c>
       <c r="E65">
-        <v>-28.53015363713815</v>
+        <v>-23.3472426797753</v>
       </c>
       <c r="F65">
-        <v>-2.638243465768972</v>
+        <v>-0.6079050210985502</v>
       </c>
       <c r="G65">
-        <v>-17.04792347133256</v>
+        <v>-11.74756941306794</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.81316553068841</v>
       </c>
       <c r="E66">
-        <v>-28.86691813519256</v>
+        <v>-23.64023494807158</v>
       </c>
       <c r="F66">
-        <v>-2.866939966701262</v>
+        <v>-0.3879320572851414</v>
       </c>
       <c r="G66">
-        <v>-17.04080978299168</v>
+        <v>-11.61110012718908</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.85627897932085</v>
       </c>
       <c r="E67">
-        <v>-28.26204986198804</v>
+        <v>-25.08693295388</v>
       </c>
       <c r="F67">
-        <v>-2.992628152728031</v>
+        <v>-0.8733884900217637</v>
       </c>
       <c r="G67">
-        <v>-17.01250596581991</v>
+        <v>-12.23800375589347</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.87236610324476</v>
       </c>
       <c r="E68">
-        <v>-27.89301545815496</v>
+        <v>-23.93621600921291</v>
       </c>
       <c r="F68">
-        <v>-2.852290289182753</v>
+        <v>-0.7855003653195417</v>
       </c>
       <c r="G68">
-        <v>-17.37467079544362</v>
+        <v>-10.99247830170073</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.86492283815533</v>
       </c>
       <c r="E69">
-        <v>-27.48735928502186</v>
+        <v>-23.94859685714988</v>
       </c>
       <c r="F69">
-        <v>-2.967718316558448</v>
+        <v>-0.2280836563017264</v>
       </c>
       <c r="G69">
-        <v>-17.28287205987504</v>
+        <v>-12.13152811628949</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.82927553966926</v>
       </c>
       <c r="E70">
-        <v>-27.83620122325473</v>
+        <v>-23.13025631922377</v>
       </c>
       <c r="F70">
-        <v>-3.107039773300491</v>
+        <v>-0.7896413739661364</v>
       </c>
       <c r="G70">
-        <v>-17.20106464395496</v>
+        <v>-11.8917659757193</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.76374920352115</v>
       </c>
       <c r="E71">
-        <v>-27.88569291568456</v>
+        <v>-23.42707514805652</v>
       </c>
       <c r="F71">
-        <v>-3.075406078922383</v>
+        <v>-0.4721049541858076</v>
       </c>
       <c r="G71">
-        <v>-17.34488386612698</v>
+        <v>-10.92265062569419</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.67373550044707</v>
       </c>
       <c r="E72">
-        <v>-27.68808389541185</v>
+        <v>-22.54993237514081</v>
       </c>
       <c r="F72">
-        <v>-3.192244815985045</v>
+        <v>-0.9545477863110453</v>
       </c>
       <c r="G72">
-        <v>-16.95944861320369</v>
+        <v>-11.99076371138931</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.5558904551</v>
       </c>
       <c r="E73">
-        <v>-27.89187881117904</v>
+        <v>-24.36834564139485</v>
       </c>
       <c r="F73">
-        <v>-3.359314095618663</v>
+        <v>-1.144090673582614</v>
       </c>
       <c r="G73">
-        <v>-16.67991150488992</v>
+        <v>-12.0227064032705</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.40987177010082</v>
       </c>
       <c r="E74">
-        <v>-27.90136596422511</v>
+        <v>-23.69251165201612</v>
       </c>
       <c r="F74">
-        <v>-3.371440566028245</v>
+        <v>-1.039045403233609</v>
       </c>
       <c r="G74">
-        <v>-17.12188712711478</v>
+        <v>-11.10282578274485</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.24347703343126</v>
       </c>
       <c r="E75">
-        <v>-28.22278799234153</v>
+        <v>-24.16543830653317</v>
       </c>
       <c r="F75">
-        <v>-3.471337532968851</v>
+        <v>-0.8537015103268306</v>
       </c>
       <c r="G75">
-        <v>-16.87609902315068</v>
+        <v>-12.17303556901646</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.05632083216956</v>
       </c>
       <c r="E76">
-        <v>-28.73265793781315</v>
+        <v>-24.18568511382146</v>
       </c>
       <c r="F76">
-        <v>-3.331470182108363</v>
+        <v>-1.423001978105208</v>
       </c>
       <c r="G76">
-        <v>-16.53151990047481</v>
+        <v>-12.08954816765795</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.851658768342386</v>
       </c>
       <c r="E77">
-        <v>-28.59193107955079</v>
+        <v>-25.40029429826278</v>
       </c>
       <c r="F77">
-        <v>-3.384102161780036</v>
+        <v>-0.8430188843003282</v>
       </c>
       <c r="G77">
-        <v>-16.46415314063785</v>
+        <v>-11.2238995770668</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.640461832849562</v>
       </c>
       <c r="E78">
-        <v>-28.52620480780346</v>
+        <v>-24.5406495489127</v>
       </c>
       <c r="F78">
-        <v>-3.493387844863971</v>
+        <v>-1.219497786626856</v>
       </c>
       <c r="G78">
-        <v>-16.06151280246761</v>
+        <v>-11.72737349436956</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.424841023236239</v>
       </c>
       <c r="E79">
-        <v>-28.98757026817892</v>
+        <v>-25.84676560762701</v>
       </c>
       <c r="F79">
-        <v>-3.725061498241923</v>
+        <v>-1.253412804832273</v>
       </c>
       <c r="G79">
-        <v>-16.18197957080107</v>
+        <v>-11.89355752269076</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.208655593702712</v>
       </c>
       <c r="E80">
-        <v>-29.2439588810712</v>
+        <v>-25.75659463318628</v>
       </c>
       <c r="F80">
-        <v>-3.558008785956361</v>
+        <v>-1.94430352509577</v>
       </c>
       <c r="G80">
-        <v>-15.58552895938988</v>
+        <v>-10.79389221048002</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.0020673310659</v>
       </c>
       <c r="E81">
-        <v>-29.73748103537513</v>
+        <v>-25.88886230200232</v>
       </c>
       <c r="F81">
-        <v>-3.621836151076868</v>
+        <v>-1.658248380091434</v>
       </c>
       <c r="G81">
-        <v>-15.44662664772469</v>
+        <v>-10.38768354386388</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.805678009791469</v>
       </c>
       <c r="E82">
-        <v>-30.363216516807</v>
+        <v>-26.68139959503272</v>
       </c>
       <c r="F82">
-        <v>-3.488651240054764</v>
+        <v>-1.477917766706398</v>
       </c>
       <c r="G82">
-        <v>-15.16608384500294</v>
+        <v>-10.61222737884136</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.621449638232711</v>
       </c>
       <c r="E83">
-        <v>-30.68371926469987</v>
+        <v>-26.81881613879548</v>
       </c>
       <c r="F83">
-        <v>-3.795005528264702</v>
+        <v>-1.618322728011303</v>
       </c>
       <c r="G83">
-        <v>-15.02900753313558</v>
+        <v>-10.48423348825054</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.456234239532167</v>
       </c>
       <c r="E84">
-        <v>-31.40062198485417</v>
+        <v>-28.38227631841767</v>
       </c>
       <c r="F84">
-        <v>-3.80682881620486</v>
+        <v>-1.641232056903126</v>
       </c>
       <c r="G84">
-        <v>-15.13698433160301</v>
+        <v>-10.03633033927854</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.307449050904378</v>
       </c>
       <c r="E85">
-        <v>-32.02640048678911</v>
+        <v>-27.72097873060357</v>
       </c>
       <c r="F85">
-        <v>-3.786051705007842</v>
+        <v>-1.592587009541128</v>
       </c>
       <c r="G85">
-        <v>-15.13782924615457</v>
+        <v>-10.16043270109986</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.173719238660571</v>
       </c>
       <c r="E86">
-        <v>-33.02968390318848</v>
+        <v>-29.89986984905319</v>
       </c>
       <c r="F86">
-        <v>-3.842094901644243</v>
+        <v>-1.647072875460265</v>
       </c>
       <c r="G86">
-        <v>-14.65257923339297</v>
+        <v>-9.869388348777109</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.057484669762689</v>
       </c>
       <c r="E87">
-        <v>-33.60072221131871</v>
+        <v>-30.57706464487122</v>
       </c>
       <c r="F87">
-        <v>-3.971181050757296</v>
+        <v>-1.564618840920408</v>
       </c>
       <c r="G87">
-        <v>-14.4922259357829</v>
+        <v>-9.990842764799956</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.953485497723463</v>
       </c>
       <c r="E88">
-        <v>-34.87056066475757</v>
+        <v>-31.95254333996101</v>
       </c>
       <c r="F88">
-        <v>-3.899988671058498</v>
+        <v>-1.724708296818038</v>
       </c>
       <c r="G88">
-        <v>-14.44590821224978</v>
+        <v>-10.56960759200573</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.859010624182408</v>
       </c>
       <c r="E89">
-        <v>-35.51809848429937</v>
+        <v>-33.37889264781597</v>
       </c>
       <c r="F89">
-        <v>-4.014653772056214</v>
+        <v>-2.287587260489913</v>
       </c>
       <c r="G89">
-        <v>-14.24348309180452</v>
+        <v>-9.910068933671106</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.775141961002812</v>
       </c>
       <c r="E90">
-        <v>-37.00564558989399</v>
+        <v>-34.46432258271448</v>
       </c>
       <c r="F90">
-        <v>-3.966712008619192</v>
+        <v>-1.701810565069854</v>
       </c>
       <c r="G90">
-        <v>-14.35625539558107</v>
+        <v>-8.861997549261071</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.696717996460171</v>
       </c>
       <c r="E91">
-        <v>-37.57373359720822</v>
+        <v>-35.87438749803786</v>
       </c>
       <c r="F91">
-        <v>-4.34772705084345</v>
+        <v>-1.860446236175571</v>
       </c>
       <c r="G91">
-        <v>-14.04148124894042</v>
+        <v>-9.077718179465204</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.621854685613795</v>
       </c>
       <c r="E92">
-        <v>-39.18985087259161</v>
+        <v>-37.85717304958531</v>
       </c>
       <c r="F92">
-        <v>-4.29094992068817</v>
+        <v>-2.41156735293211</v>
       </c>
       <c r="G92">
-        <v>-13.87800915023811</v>
+        <v>-9.374593262499085</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.551784023683416</v>
       </c>
       <c r="E93">
-        <v>-40.24304033679251</v>
+        <v>-38.67088095860158</v>
       </c>
       <c r="F93">
-        <v>-4.241222197130712</v>
+        <v>-2.358224634028836</v>
       </c>
       <c r="G93">
-        <v>-14.40709136120155</v>
+        <v>-9.29502035846099</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.482632243656183</v>
       </c>
       <c r="E94">
-        <v>-42.00157585548013</v>
+        <v>-39.51121176630893</v>
       </c>
       <c r="F94">
-        <v>-4.535915557411442</v>
+        <v>-2.388107159717425</v>
       </c>
       <c r="G94">
-        <v>-14.32264256192612</v>
+        <v>-9.843056545762567</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.41411569118236</v>
       </c>
       <c r="E95">
-        <v>-42.94832580236774</v>
+        <v>-41.12989442221767</v>
       </c>
       <c r="F95">
-        <v>-4.534488280376419</v>
+        <v>-2.118811544006528</v>
       </c>
       <c r="G95">
-        <v>-15.17356995199082</v>
+        <v>-9.920552436553532</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.347604712799591</v>
       </c>
       <c r="E96">
-        <v>-44.78910520174566</v>
+        <v>-43.52158532699873</v>
       </c>
       <c r="F96">
-        <v>-4.720262095965249</v>
+        <v>-2.733941438344788</v>
       </c>
       <c r="G96">
-        <v>-14.8834131700999</v>
+        <v>-10.70122395119818</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.280515362867215</v>
       </c>
       <c r="E97">
-        <v>-46.11918141643456</v>
+        <v>-46.49949624902074</v>
       </c>
       <c r="F97">
-        <v>-4.769328782335273</v>
+        <v>-2.631762319209469</v>
       </c>
       <c r="G97">
-        <v>-15.44927295291238</v>
+        <v>-9.971486838820791</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.212994057567329</v>
       </c>
       <c r="E98">
-        <v>-47.40487179313727</v>
+        <v>-46.37139930476576</v>
       </c>
       <c r="F98">
-        <v>-4.772948747885506</v>
+        <v>-2.834922738215659</v>
       </c>
       <c r="G98">
-        <v>-15.18068856216403</v>
+        <v>-10.37357100993671</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.144656991056648</v>
       </c>
       <c r="E99">
-        <v>-49.2472508759584</v>
+        <v>-47.91906416704921</v>
       </c>
       <c r="F99">
-        <v>-4.882377738530127</v>
+        <v>-2.535772761307868</v>
       </c>
       <c r="G99">
-        <v>-15.31620465317988</v>
+        <v>-11.23408120756576</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.076299466938845</v>
       </c>
       <c r="E100">
-        <v>-51.00626188441682</v>
+        <v>-49.60227644544874</v>
       </c>
       <c r="F100">
-        <v>-5.073456418966486</v>
+        <v>-3.252277430033328</v>
       </c>
       <c r="G100">
-        <v>-15.73347759889446</v>
+        <v>-11.09030792249557</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.003203969939245</v>
       </c>
       <c r="E101">
-        <v>-52.83712845419196</v>
+        <v>-52.755677056453</v>
       </c>
       <c r="F101">
-        <v>-4.931351647751036</v>
+        <v>-2.757953324249737</v>
       </c>
       <c r="G101">
-        <v>-15.99601962014109</v>
+        <v>-10.77071694260566</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.929068371027634</v>
       </c>
       <c r="E102">
-        <v>-54.73168687876647</v>
+        <v>-53.21672892000343</v>
       </c>
       <c r="F102">
-        <v>-5.302595268091871</v>
+        <v>-2.76482794532557</v>
       </c>
       <c r="G102">
-        <v>-16.07112842224756</v>
+        <v>-11.20844174230026</v>
       </c>
     </row>
   </sheetData>
